--- a/content/Question Bank/MCQ/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 2.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 2.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 2.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 2.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 2.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 2.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 2.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 2.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,26 +643,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Python programs run measurably slower when using short variable names</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Vague variable names make the code's intent hard to recover later</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>Variable names that start with a letter are considered invalid in Python</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Python programs run measurably slower when using short variable names</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>The names x1 and y2 happen to be reserved Python keywords</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Vague variable names make the code's intent hard to recover later</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -721,7 +721,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The values 0.1 and 0.2 are silently treated as ordinary text strings, not numbers</t>
+          <t>`The == operator` simply does not work correctly on floating-point numbers at all</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>`The == operator` simply does not work correctly on floating-point numbers at all</t>
+          <t>The values 0.1 and 0.2 are silently treated as plain text, not real numeric values at all</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>53 (as a number)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Error</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>53 (as a number)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -877,14 +877,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>It raises a `ValueError`</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>It returns "abc" unchanged</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>It raises a `ValueError`</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>It returns `None`</t>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -965,16 +965,16 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>The remainder of a division</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>The quotient of a division</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>The remainder of a division</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1111,22 +1111,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>The value of discount_percent itself must be incorrect</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Dividing by 100 at the end is the actual source of the bug</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>The added parentheses force subtraction first, making the result always 0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Python evaluates the two expressions in exactly the same way</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>The value of discount_percent itself must be incorrect</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>The added parentheses force subtraction first, making the result always 0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Dividing by 100 at the end is the actual source of the bug</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1189,26 +1189,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>age is a string, and a string cannot be added to an integer</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>The `input()` function never works properly inside `print()`</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>The + operator does not work on variables at all</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>The variable age must first be declared as global</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>age is a string, and a string cannot be added to an integer</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>The + operator does not work on variables at all</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1267,26 +1267,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>It runs first, immediately before `check_password()` is even called</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>It is never called, because or stops as soon as it finds a `True` value</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>It runs first, immediately before `check_password()` is even called</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>It raises an error, because the code becomes unreachable</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>It still runs afterward, but its returned result is simply ignored</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>It raises an error, because the code becomes unreachable</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1345,26 +1345,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>`True` and `False`</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>yes and no answers</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>0 and 1 only</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>on and off states</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>`True` and `False`</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>yes and no answers</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1524,14 +1524,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Creates a variable named age and stores 25 in it</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Prints the number 25 directly to the screen</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Creates a variable named age and stores 25 in it</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Declares a constant value that can never change</t>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1602,26 +1602,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1685,21 +1685,21 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1834,26 +1834,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>`True`</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>`False`</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>`True`</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1912,26 +1912,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>or</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>not</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>xor</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1990,26 +1990,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>student_name</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>total-marks</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2nd_value</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>total-marks</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2068,26 +2068,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Converts the number 42 back into text</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Adds the number 42 to another number</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Checks whether the given text contains only digits</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>Converts the text "42" into the integer 42</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Converts the number 42 back into text</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Adds the number 42 to another number</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Checks whether the given text contains only digits</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2146,26 +2146,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2224,26 +2224,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>`True`</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>`False`</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>`True`</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2408,17 +2408,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>`True`</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Error</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2481,26 +2481,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>50, because both operations apply to the original 100</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>35, because each step updates balance before the next runs</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>70, because only the last operation counts</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>17, because divide happens first</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>50, because both operations apply to the original 100</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>35, because each step updates balance before the next runs</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2637,26 +2637,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>An integer</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>A float</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>A string</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>An integer</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>A boolean</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>A float</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2715,26 +2715,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>complex</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>It works fine and stores 200, automatically rounded up to the nearest whole number</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>It silently stores the value 0 instead, with no error at all</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>It works correctly and stores just the whole number 199</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>It works fine and stores 200 after being automatically rounded up</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -2873,22 +2873,22 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>:=</t>
-        </is>
-      </c>
-      <c r="P8">
+      <c r="N8">
         <f>=</f>
         <v/>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>:=</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>`True`</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>`None`</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>`True`</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Error</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -3025,26 +3025,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>64, evaluated left to right</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>18, by adding the exponents</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>36, by multiplying the exponents</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>64, evaluated left to right</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>18, by adding the exponents</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3282,22 +3282,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>`print("Hello, " + f.name)`</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>`print(fstring("Hello, name"))`</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>`print(f"Hello, {name}")`</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>`print("Hello, {name}")`</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>`print("Hello, " + f.name)`</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>`print(f"Hello, {name}")`</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>`print(fstring("Hello, name"))`</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3360,26 +3360,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>`x=6`, `y=6`</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>`x=5`, `y=6`</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>`x=6`, `y=5`</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>`x=5`, `y=5`</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>`x=6`, `y=6`</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3438,26 +3438,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>`True`</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>"10"</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>`True`</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3516,26 +3516,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3594,26 +3594,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>9.8</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3672,26 +3672,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>The number of full boxes (8)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>The leftover cookies that don't fill a box (2)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>The total boxes needed (9)</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>An error, since 50 is not divisible by 6</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>The number of full boxes (8)</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>The total boxes needed (9)</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3750,26 +3750,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>`True`</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>`False`</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>`True`</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>-=</t>
         </is>
       </c>
       <c r="N9">
@@ -3841,11 +3841,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-=</t>
+          <t>--</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3909,21 +3909,21 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Parentheses</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Parentheses</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Addition</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3982,26 +3982,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>Price: 49.50</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Price: 49.5</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Price: 49</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Price: 49.5</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Price: 49.50</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - MCQ.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A teammate named a variable x1 for student marks and y2 for attendance percentage. Six months later, fixing a bug in this code takes much longer than expected. What is the most likely reason?</t>
+          <t>A teammate named a variable `x1` for student marks and `y2` for attendance percentage. Six months later, fixing a bug in this code takes much longer than expected. What is the most likely reason?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uninformative names like x1 and y2 carry no meaning, so anyone reading the code later, including the original author, must work hard to infer what each variable represents, slowing debugging.</t>
+          <t>Uninformative names like `x1` and `y2` carry no meaning, so anyone reading the code later, including the original author, must work hard to infer what each variable represents, slowing debugging.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>The names x1 and y2 happen to be reserved Python keywords</t>
+          <t>The names `x1` and `y2` happen to be reserved Python keywords</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A program calculates a discount as price - price * discount_percent / 100 and gets a sensible result, but a teammate rewrites it as (price - price) * discount_percent / 100 'to make it clearer' and the discount always comes out as 0. What went wrong?</t>
+          <t>A program calculates a discount as price - price * `discount_percent` / 100 and gets a sensible result, but a teammate rewrites it as (price - price) * `discount_percent` / 100 'to make it clearer' and the discount always comes out as 0. What went wrong?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The value of discount_percent itself must be incorrect</t>
+          <t>The value of `discount_percent` itself must be incorrect</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Variable names cannot start with a digit, cannot contain hyphens, and cannot be a reserved keyword such as class; student_name follows all the naming rules.</t>
+          <t>Variable names cannot start with a digit, cannot contain hyphens, and cannot be a reserved keyword such as class; `student_name` follows all the naming rules.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>`student_name`</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - Unit 2" sheetId="1" r:id="Rc74a7e48418c4da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - Unit 2" sheetId="1" r:id="R2a8de5d9644840bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,12 +26,27 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -45,7 +60,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -57,6 +72,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -394,55 +418,55 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>title</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>description</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>explanation</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>score</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="8" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="8" t="str">
         <x:v>difficulty</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="8" t="str">
         <x:v>bloomTaxonomy</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="8" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="I1" s="3" t="str">
+      <x:c r="I1" s="8" t="str">
         <x:v>subjects</x:v>
       </x:c>
-      <x:c r="J1" s="3" t="str">
+      <x:c r="J1" s="8" t="str">
         <x:v>topics</x:v>
       </x:c>
-      <x:c r="K1" s="3" t="str">
+      <x:c r="K1" s="8" t="str">
         <x:v>subTopics</x:v>
       </x:c>
-      <x:c r="L1" s="3" t="str">
+      <x:c r="L1" s="8" t="str">
         <x:v>companies</x:v>
       </x:c>
-      <x:c r="M1" s="3" t="str">
+      <x:c r="M1" s="8" t="str">
         <x:v>option1</x:v>
       </x:c>
-      <x:c r="N1" s="3" t="str">
+      <x:c r="N1" s="8" t="str">
         <x:v>option2</x:v>
       </x:c>
-      <x:c r="O1" s="3" t="str">
+      <x:c r="O1" s="8" t="str">
         <x:v>option3</x:v>
       </x:c>
-      <x:c r="P1" s="3" t="str">
+      <x:c r="P1" s="8" t="str">
         <x:v>option4</x:v>
       </x:c>
-      <x:c r="Q1" s="3" t="str">
+      <x:c r="Q1" s="8" t="str">
         <x:v>answer</x:v>
       </x:c>
     </x:row>
@@ -468,7 +492,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F2" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
         <x:v>analyze</x:v>
@@ -738,7 +762,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
         <x:v>apply</x:v>
@@ -848,7 +872,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
         <x:v>apply</x:v>
@@ -1017,7 +1041,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
         <x:v>apply</x:v>
@@ -1072,7 +1096,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
         <x:v>analyze</x:v>
@@ -1444,7 +1468,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
         <x:v>apply</x:v>
@@ -1715,7 +1739,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F25" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
         <x:v>analyze</x:v>
@@ -1770,7 +1794,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -1821,7 +1845,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F27" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
         <x:v>analyze</x:v>
@@ -1876,7 +1900,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
         <x:v>apply</x:v>
@@ -1928,7 +1952,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F29" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
         <x:v>apply</x:v>
@@ -2036,7 +2060,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F31" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
         <x:v>analyze</x:v>
@@ -2088,7 +2112,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
         <x:v>apply</x:v>
@@ -2139,7 +2163,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
         <x:v>apply</x:v>
@@ -2245,7 +2269,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
         <x:v>analyze</x:v>
@@ -2408,7 +2432,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
         <x:v>apply</x:v>
@@ -2459,7 +2483,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
         <x:v>apply</x:v>
@@ -2570,7 +2594,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -2607,7 +2631,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24d9e88b1df84151"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64a92508301e4132"/>
   </x:tableParts>
 </x:worksheet>
 </file>